--- a/conception/todo.xlsx
+++ b/conception/todo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\S5\S3 - S5\Pharmacie\conception\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{681C9EF2-137B-4074-8502-4A30235366BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F68637B-2AA4-4D40-8E09-C7C862D1A863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00740D2D-B267-42E1-9501-807A4F2BA37B}"/>
   </bookViews>
@@ -96,9 +96,6 @@
     <t>personne</t>
   </si>
   <si>
-    <t>Antonia</t>
-  </si>
-  <si>
     <t>10min</t>
   </si>
   <si>
@@ -557,6 +554,9 @@
     list
     search
  </t>
+  </si>
+  <si>
+    <t>Adrian</t>
   </si>
 </sst>
 </file>
@@ -699,16 +699,16 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1034,194 +1034,194 @@
     <col min="4" max="4" width="20.109375" customWidth="1"/>
     <col min="5" max="5" width="23.21875" customWidth="1"/>
     <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="51.88671875" customWidth="1"/>
+    <col min="7" max="7" width="59.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
       <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="14"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="15" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
       <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
       <c r="H9" s="14"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
       <c r="H12" s="14"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
       <c r="H15" s="14"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A17" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>0</v>
@@ -1247,16 +1247,16 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="D18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" t="s">
         <v>23</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
       </c>
       <c r="F18" s="12">
         <v>100</v>
@@ -1265,13 +1265,13 @@
     <row r="19" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="C19" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" t="s">
         <v>23</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
       </c>
       <c r="F19" s="12">
         <v>100</v>
@@ -1280,13 +1280,13 @@
     <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="C20" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" t="s">
         <v>23</v>
-      </c>
-      <c r="E20" t="s">
-        <v>24</v>
       </c>
       <c r="F20" s="12">
         <v>100</v>
@@ -1295,13 +1295,13 @@
     <row r="21" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
       <c r="C21" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" t="s">
         <v>23</v>
-      </c>
-      <c r="E21" t="s">
-        <v>24</v>
       </c>
       <c r="F21" s="12">
         <v>100</v>
@@ -1310,13 +1310,13 @@
     <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="C22" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" t="s">
         <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
       </c>
       <c r="F22" s="12">
         <v>100</v>
@@ -1325,13 +1325,13 @@
     <row r="23" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="C23" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" t="s">
         <v>23</v>
-      </c>
-      <c r="E23" t="s">
-        <v>24</v>
       </c>
       <c r="F23" s="12">
         <v>100</v>
@@ -1340,13 +1340,13 @@
     <row r="24" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="C24" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" t="s">
         <v>23</v>
-      </c>
-      <c r="E24" t="s">
-        <v>24</v>
       </c>
       <c r="F24" s="12">
         <v>100</v>
@@ -1355,13 +1355,13 @@
     <row r="25" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="C25" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" t="s">
         <v>23</v>
-      </c>
-      <c r="E25" t="s">
-        <v>24</v>
       </c>
       <c r="F25" s="12">
         <v>100</v>
@@ -1370,13 +1370,13 @@
     <row r="26" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="C26" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s">
         <v>23</v>
-      </c>
-      <c r="E26" t="s">
-        <v>24</v>
       </c>
       <c r="F26" s="12">
         <v>100</v>
@@ -1384,19 +1384,19 @@
     </row>
     <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="E27" t="s">
         <v>27</v>
-      </c>
-      <c r="E27" t="s">
-        <v>28</v>
       </c>
       <c r="F27" s="12">
         <v>100</v>
@@ -1405,16 +1405,16 @@
     <row r="28" spans="1:7" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D28" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
         <v>27</v>
-      </c>
-      <c r="E28" t="s">
-        <v>28</v>
       </c>
       <c r="F28" s="12">
         <v>100</v>
@@ -1425,16 +1425,16 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" s="12">
         <v>100</v>
@@ -1442,19 +1442,19 @@
     </row>
     <row r="30" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D30" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
         <v>27</v>
-      </c>
-      <c r="E30" t="s">
-        <v>28</v>
       </c>
       <c r="F30" s="12">
         <v>100</v>
@@ -1465,16 +1465,16 @@
         <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" s="12">
         <v>100</v>
@@ -1482,19 +1482,19 @@
     </row>
     <row r="32" spans="1:7" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D32" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
         <v>27</v>
-      </c>
-      <c r="E32" t="s">
-        <v>28</v>
       </c>
       <c r="F32" s="12">
         <v>100</v>
@@ -1505,16 +1505,16 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F33" s="12">
         <v>100</v>
@@ -1522,19 +1522,19 @@
     </row>
     <row r="34" spans="1:6" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D34" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
         <v>27</v>
-      </c>
-      <c r="E34" t="s">
-        <v>28</v>
       </c>
       <c r="F34" s="13">
         <v>60</v>
@@ -1545,16 +1545,16 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F35" s="13">
         <v>60</v>
@@ -1563,13 +1563,13 @@
     <row r="36" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
       <c r="C36" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" t="s">
         <v>23</v>
-      </c>
-      <c r="E36" t="s">
-        <v>24</v>
       </c>
       <c r="F36" s="13">
         <v>0</v>
@@ -1577,19 +1577,19 @@
     </row>
     <row r="37" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="D37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" t="s">
         <v>27</v>
-      </c>
-      <c r="E37" t="s">
-        <v>28</v>
       </c>
       <c r="F37" s="12">
         <v>100</v>
@@ -1600,16 +1600,16 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F38" s="12">
         <v>100</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="39" spans="1:6" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" t="s">
         <v>23</v>
-      </c>
-      <c r="E39" t="s">
-        <v>24</v>
       </c>
       <c r="F39" s="12">
         <v>100</v>
@@ -1631,6 +1631,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D12:G12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A15:C15"/>
@@ -1647,12 +1653,6 @@
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="D9:G9"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
